--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/105.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/105.xlsx
@@ -426,13 +426,13 @@
         <v>-13.59935686360149</v>
       </c>
       <c r="E2">
-        <v>-3.326188877711518</v>
+        <v>-6.518301148770338</v>
       </c>
       <c r="F2">
-        <v>-4.474321438858996</v>
+        <v>-3.988940915071452</v>
       </c>
       <c r="G2">
-        <v>-17.02428295363806</v>
+        <v>-16.20749522655245</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.92848090328355</v>
       </c>
       <c r="E3">
-        <v>-4.660395060695405</v>
+        <v>-6.32816863908429</v>
       </c>
       <c r="F3">
-        <v>-4.930530891537103</v>
+        <v>-3.708997930781756</v>
       </c>
       <c r="G3">
-        <v>-16.83112586360374</v>
+        <v>-16.47569741814374</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.27193689583274</v>
       </c>
       <c r="E4">
-        <v>-5.300359007459379</v>
+        <v>-6.90469319347481</v>
       </c>
       <c r="F4">
-        <v>-4.282158522344362</v>
+        <v>-3.889425586462984</v>
       </c>
       <c r="G4">
-        <v>-16.86883794311435</v>
+        <v>-15.90411186751533</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.70515179811196</v>
       </c>
       <c r="E5">
-        <v>-4.424162685611273</v>
+        <v>-7.613431074993275</v>
       </c>
       <c r="F5">
-        <v>-4.301343535803995</v>
+        <v>-3.356324836031419</v>
       </c>
       <c r="G5">
-        <v>-16.74664736253262</v>
+        <v>-16.33296986830914</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.19051897168185</v>
       </c>
       <c r="E6">
-        <v>-6.77064583437376</v>
+        <v>-10.28688363253159</v>
       </c>
       <c r="F6">
-        <v>-3.893144919805393</v>
+        <v>-3.01331630663005</v>
       </c>
       <c r="G6">
-        <v>-16.89970712499528</v>
+        <v>-16.69129007529769</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.72231743349317</v>
       </c>
       <c r="E7">
-        <v>-8.114905229654676</v>
+        <v>-10.18529637511752</v>
       </c>
       <c r="F7">
-        <v>-3.850226489496984</v>
+        <v>-2.968384986103118</v>
       </c>
       <c r="G7">
-        <v>-17.3360982721637</v>
+        <v>-15.96515170616841</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.26101847559862</v>
       </c>
       <c r="E8">
-        <v>-7.218856077756942</v>
+        <v>-11.79581645662743</v>
       </c>
       <c r="F8">
-        <v>-3.366946751606271</v>
+        <v>-2.478102100654332</v>
       </c>
       <c r="G8">
-        <v>-16.70376917670798</v>
+        <v>-15.89867429646708</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.797715980255177</v>
       </c>
       <c r="E9">
-        <v>-8.833229890647377</v>
+        <v>-11.09290219268282</v>
       </c>
       <c r="F9">
-        <v>-3.31238174799572</v>
+        <v>-2.510819881161395</v>
       </c>
       <c r="G9">
-        <v>-15.99088457664517</v>
+        <v>-16.30124325513354</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.31238172686448</v>
       </c>
       <c r="E10">
-        <v>-10.31194420769003</v>
+        <v>-12.2668728513793</v>
       </c>
       <c r="F10">
-        <v>-3.153028466931246</v>
+        <v>-2.833452450254719</v>
       </c>
       <c r="G10">
-        <v>-16.39438048806262</v>
+        <v>-15.92128201195476</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.797531702618196</v>
       </c>
       <c r="E11">
-        <v>-11.0622489521249</v>
+        <v>-12.98690021859889</v>
       </c>
       <c r="F11">
-        <v>-2.847652749345507</v>
+        <v>-2.766849697980913</v>
       </c>
       <c r="G11">
-        <v>-15.8905618046231</v>
+        <v>-14.77250119128165</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.262355741818363</v>
       </c>
       <c r="E12">
-        <v>-10.90202248478551</v>
+        <v>-13.49992198197985</v>
       </c>
       <c r="F12">
-        <v>-2.915264322287448</v>
+        <v>-2.290963491156429</v>
       </c>
       <c r="G12">
-        <v>-16.30808946330875</v>
+        <v>-15.45295237669622</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.708786650584688</v>
       </c>
       <c r="E13">
-        <v>-12.5399851187819</v>
+        <v>-14.35670473575707</v>
       </c>
       <c r="F13">
-        <v>-2.728565983034038</v>
+        <v>-2.688981253677629</v>
       </c>
       <c r="G13">
-        <v>-15.49293549044677</v>
+        <v>-16.01237994883166</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.159811873094526</v>
       </c>
       <c r="E14">
-        <v>-13.9635833786772</v>
+        <v>-14.70596782207266</v>
       </c>
       <c r="F14">
-        <v>-2.460133373337756</v>
+        <v>-2.362687156507809</v>
       </c>
       <c r="G14">
-        <v>-15.14584630920019</v>
+        <v>-14.73505064486865</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.636583763041928</v>
       </c>
       <c r="E15">
-        <v>-13.95976134661473</v>
+        <v>-15.86863540964599</v>
       </c>
       <c r="F15">
-        <v>-2.286169613350394</v>
+        <v>-1.793648159590134</v>
       </c>
       <c r="G15">
-        <v>-14.68987825098529</v>
+        <v>-13.22970255107003</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.156218978797011</v>
       </c>
       <c r="E16">
-        <v>-14.34184681253791</v>
+        <v>-17.77516825161529</v>
       </c>
       <c r="F16">
-        <v>-1.774737127253871</v>
+        <v>-1.716173266206836</v>
       </c>
       <c r="G16">
-        <v>-14.52101063357261</v>
+        <v>-12.70416006780181</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.745998456766864</v>
       </c>
       <c r="E17">
-        <v>-16.22136730705145</v>
+        <v>-18.43129885058665</v>
       </c>
       <c r="F17">
-        <v>-1.868513897477745</v>
+        <v>-1.58679241144501</v>
       </c>
       <c r="G17">
-        <v>-13.77663446906748</v>
+        <v>-11.27866895350149</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.415860706658218</v>
       </c>
       <c r="E18">
-        <v>-17.34960490674447</v>
+        <v>-19.18292138095775</v>
       </c>
       <c r="F18">
-        <v>-1.389811069682652</v>
+        <v>-1.450350603859198</v>
       </c>
       <c r="G18">
-        <v>-13.13085959290401</v>
+        <v>-11.43410237711581</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.17396991628511</v>
       </c>
       <c r="E19">
-        <v>-18.67363108015911</v>
+        <v>-19.58444305732185</v>
       </c>
       <c r="F19">
-        <v>-1.021560643548052</v>
+        <v>-0.777978755223888</v>
       </c>
       <c r="G19">
-        <v>-12.80242036995292</v>
+        <v>-13.279268038884</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.021650289328662</v>
       </c>
       <c r="E20">
-        <v>-18.58945580530454</v>
+        <v>-21.83269454790995</v>
       </c>
       <c r="F20">
-        <v>-0.6650415189820702</v>
+        <v>-0.8373154647576578</v>
       </c>
       <c r="G20">
-        <v>-11.90029671050152</v>
+        <v>-11.52332157939917</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.941869469875406</v>
       </c>
       <c r="E21">
-        <v>-19.7580466368799</v>
+        <v>-21.76672373856621</v>
       </c>
       <c r="F21">
-        <v>-0.6057380672725247</v>
+        <v>-0.8306346013533765</v>
       </c>
       <c r="G21">
-        <v>-12.30737463219246</v>
+        <v>-11.76020435491618</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.921160699510388</v>
       </c>
       <c r="E22">
-        <v>-20.2726261953195</v>
+        <v>-21.99243194005652</v>
       </c>
       <c r="F22">
-        <v>-0.3697144154297952</v>
+        <v>-0.1027736567058569</v>
       </c>
       <c r="G22">
-        <v>-12.13781511076207</v>
+        <v>-11.1320647548404</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.932375172393171</v>
       </c>
       <c r="E23">
-        <v>-21.47393978007429</v>
+        <v>-23.00869396296187</v>
       </c>
       <c r="F23">
-        <v>-0.3009182304631056</v>
+        <v>0.08943043616257851</v>
       </c>
       <c r="G23">
-        <v>-11.85571359372415</v>
+        <v>-10.82831889106673</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.947446091423578</v>
       </c>
       <c r="E24">
-        <v>-20.26069366630929</v>
+        <v>-23.77132068517161</v>
       </c>
       <c r="F24">
-        <v>0.1085069657670044</v>
+        <v>0.04934367203097521</v>
       </c>
       <c r="G24">
-        <v>-11.46065957343184</v>
+        <v>-11.15113680769214</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.945843094722745</v>
       </c>
       <c r="E25">
-        <v>-21.60206842364732</v>
+        <v>-24.03999051957268</v>
       </c>
       <c r="F25">
-        <v>-0.08313807891328089</v>
+        <v>0.02821941067788614</v>
       </c>
       <c r="G25">
-        <v>-12.14875315322382</v>
+        <v>-11.13427619926064</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.902685679969907</v>
       </c>
       <c r="E26">
-        <v>-21.64969438478598</v>
+        <v>-23.18342060407382</v>
       </c>
       <c r="F26">
-        <v>-0.004974273456766956</v>
+        <v>0.6802350953290952</v>
       </c>
       <c r="G26">
-        <v>-12.55700962912674</v>
+        <v>-11.87271655561385</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.807482536052791</v>
       </c>
       <c r="E27">
-        <v>-21.13256076700606</v>
+        <v>-24.09902823521068</v>
       </c>
       <c r="F27">
-        <v>-0.2047263087181867</v>
+        <v>0.4922880039613611</v>
       </c>
       <c r="G27">
-        <v>-12.00713794669042</v>
+        <v>-10.23728057484957</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.654630289038057</v>
       </c>
       <c r="E28">
-        <v>-22.41405098406666</v>
+        <v>-23.33912765435356</v>
       </c>
       <c r="F28">
-        <v>0.03171385778030329</v>
+        <v>0.3591363454148741</v>
       </c>
       <c r="G28">
-        <v>-11.52077245933393</v>
+        <v>-11.64795368731611</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.445067905225917</v>
       </c>
       <c r="E29">
-        <v>-21.16378006681494</v>
+        <v>-25.85717204089664</v>
       </c>
       <c r="F29">
-        <v>0.01433426906427079</v>
+        <v>0.2815759319121426</v>
       </c>
       <c r="G29">
-        <v>-11.65716031446082</v>
+        <v>-12.02249556744709</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.190738411738313</v>
       </c>
       <c r="E30">
-        <v>-21.23829610661116</v>
+        <v>-24.50831624449794</v>
       </c>
       <c r="F30">
-        <v>0.01638833563659575</v>
+        <v>0.4688919164725742</v>
       </c>
       <c r="G30">
-        <v>-12.46799237012128</v>
+        <v>-11.00574757924397</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.901357235289804</v>
       </c>
       <c r="E31">
-        <v>-21.17068146120263</v>
+        <v>-23.01002080584611</v>
       </c>
       <c r="F31">
-        <v>0.124719363223358</v>
+        <v>0.3861504090674825</v>
       </c>
       <c r="G31">
-        <v>-12.01551031635923</v>
+        <v>-12.04374926980922</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.593567070490018</v>
       </c>
       <c r="E32">
-        <v>-21.52940452972024</v>
+        <v>-23.31440218627168</v>
       </c>
       <c r="F32">
-        <v>0.04086371870675469</v>
+        <v>0.8872983089491412</v>
       </c>
       <c r="G32">
-        <v>-11.42702443075285</v>
+        <v>-10.67333239110021</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.286518997767438</v>
       </c>
       <c r="E33">
-        <v>-21.11339173653159</v>
+        <v>-22.95607762346675</v>
       </c>
       <c r="F33">
-        <v>0.0703198568809707</v>
+        <v>0.2414883759275816</v>
       </c>
       <c r="G33">
-        <v>-11.22977219588645</v>
+        <v>-11.3782865793237</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.995013150382153</v>
       </c>
       <c r="E34">
-        <v>-20.79706424167379</v>
+        <v>-22.98948417622133</v>
       </c>
       <c r="F34">
-        <v>-0.1444924297833205</v>
+        <v>-0.02648891831801185</v>
       </c>
       <c r="G34">
-        <v>-10.97846868400038</v>
+        <v>-11.67142545518954</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.737397434637138</v>
       </c>
       <c r="E35">
-        <v>-20.02881315474653</v>
+        <v>-21.93141528127716</v>
       </c>
       <c r="F35">
-        <v>-0.1233396617237535</v>
+        <v>0.02140947524149652</v>
       </c>
       <c r="G35">
-        <v>-10.28622368010215</v>
+        <v>-10.24015081783212</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.52429386117918</v>
       </c>
       <c r="E36">
-        <v>-18.37035917586543</v>
+        <v>-22.97225786109615</v>
       </c>
       <c r="F36">
-        <v>0.1509273205650077</v>
+        <v>-0.2080291274048357</v>
       </c>
       <c r="G36">
-        <v>-10.85272423278224</v>
+        <v>-10.96663679424302</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.362302168694109</v>
       </c>
       <c r="E37">
-        <v>-18.39719944130889</v>
+        <v>-22.96877999305826</v>
       </c>
       <c r="F37">
-        <v>-0.07067906447651875</v>
+        <v>-0.1614531282847193</v>
       </c>
       <c r="G37">
-        <v>-10.67898349233575</v>
+        <v>-10.76491863344415</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.257597429852358</v>
       </c>
       <c r="E38">
-        <v>-18.25539933470671</v>
+        <v>-21.8536251547734</v>
       </c>
       <c r="F38">
-        <v>-0.3487778232276857</v>
+        <v>-0.0470905567190059</v>
       </c>
       <c r="G38">
-        <v>-10.11809100379919</v>
+        <v>-10.06545995081586</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.205583733002395</v>
       </c>
       <c r="E39">
-        <v>-17.55456364033163</v>
+        <v>-20.54418066766346</v>
       </c>
       <c r="F39">
-        <v>-0.1804813548587242</v>
+        <v>0.2961238544513694</v>
       </c>
       <c r="G39">
-        <v>-10.74264197251039</v>
+        <v>-9.859017641532443</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.203723158967987</v>
       </c>
       <c r="E40">
-        <v>-17.87355387790593</v>
+        <v>-20.77323993991944</v>
       </c>
       <c r="F40">
-        <v>-0.2532106734664077</v>
+        <v>0.007677953101678789</v>
       </c>
       <c r="G40">
-        <v>-10.10268703540496</v>
+        <v>-10.65391935205793</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.244119980840415</v>
       </c>
       <c r="E41">
-        <v>-16.07857093616758</v>
+        <v>-19.85766400810063</v>
       </c>
       <c r="F41">
-        <v>-0.4557579496685781</v>
+        <v>0.1309536215594854</v>
       </c>
       <c r="G41">
-        <v>-10.35405675820182</v>
+        <v>-11.23007014498499</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.315184436321714</v>
       </c>
       <c r="E42">
-        <v>-16.11585839114674</v>
+        <v>-19.24766950231942</v>
       </c>
       <c r="F42">
-        <v>-0.8906721007547282</v>
+        <v>0.3807127548068212</v>
       </c>
       <c r="G42">
-        <v>-9.577303458322621</v>
+        <v>-9.939540040684136</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.41038028745661</v>
       </c>
       <c r="E43">
-        <v>-15.84249705767372</v>
+        <v>-19.20528751408163</v>
       </c>
       <c r="F43">
-        <v>-0.963513862482408</v>
+        <v>-0.009566228758583635</v>
       </c>
       <c r="G43">
-        <v>-9.232053285123108</v>
+        <v>-9.26338759865231</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.519109383036693</v>
       </c>
       <c r="E44">
-        <v>-15.72030071505074</v>
+        <v>-18.64519226339094</v>
       </c>
       <c r="F44">
-        <v>-1.023400117968835</v>
+        <v>-0.5699740284371133</v>
       </c>
       <c r="G44">
-        <v>-9.476484104469657</v>
+        <v>-8.811660349273216</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.635046289084181</v>
       </c>
       <c r="E45">
-        <v>-15.13339689823464</v>
+        <v>-18.4797399370467</v>
       </c>
       <c r="F45">
-        <v>-1.14448868855742</v>
+        <v>-0.04161251795750085</v>
       </c>
       <c r="G45">
-        <v>-9.414298817059986</v>
+        <v>-9.188602374920173</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.75291910887154</v>
       </c>
       <c r="E46">
-        <v>-13.87724802172097</v>
+        <v>-17.79554638464981</v>
       </c>
       <c r="F46">
-        <v>-1.484735234842262</v>
+        <v>0.1293026081426397</v>
       </c>
       <c r="G46">
-        <v>-9.452244290031112</v>
+        <v>-9.535809080533395</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.863324697816038</v>
       </c>
       <c r="E47">
-        <v>-12.90811382781344</v>
+        <v>-17.69165413396583</v>
       </c>
       <c r="F47">
-        <v>-1.21603497884627</v>
+        <v>-0.459312577595782</v>
       </c>
       <c r="G47">
-        <v>-10.02642199781677</v>
+        <v>-9.395488297305848</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.962112797188698</v>
       </c>
       <c r="E48">
-        <v>-12.60239654755562</v>
+        <v>-17.4247232335837</v>
       </c>
       <c r="F48">
-        <v>-1.62374818898179</v>
+        <v>-0.3262923666402764</v>
       </c>
       <c r="G48">
-        <v>-9.731687439000995</v>
+        <v>-10.42458462037045</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.046290306791803</v>
       </c>
       <c r="E49">
-        <v>-13.01349141797193</v>
+        <v>-15.54031651561588</v>
       </c>
       <c r="F49">
-        <v>-1.639799048434769</v>
+        <v>-0.912667400361309</v>
       </c>
       <c r="G49">
-        <v>-8.900723955916229</v>
+        <v>-9.462146131739074</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.116651901431338</v>
       </c>
       <c r="E50">
-        <v>-12.25167076413555</v>
+        <v>-16.25542596006314</v>
       </c>
       <c r="F50">
-        <v>-1.61478203794153</v>
+        <v>-0.7336056910321479</v>
       </c>
       <c r="G50">
-        <v>-9.59061847248157</v>
+        <v>-9.334600743747572</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.183091820876756</v>
       </c>
       <c r="E51">
-        <v>-10.12362308760705</v>
+        <v>-15.8087735117386</v>
       </c>
       <c r="F51">
-        <v>-1.697715965615347</v>
+        <v>-0.6548867966522725</v>
       </c>
       <c r="G51">
-        <v>-8.77448954395828</v>
+        <v>-9.543658384007008</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.252010663548555</v>
       </c>
       <c r="E52">
-        <v>-10.18394688986323</v>
+        <v>-14.46940486838597</v>
       </c>
       <c r="F52">
-        <v>-1.883452203525128</v>
+        <v>-0.8222330414719703</v>
       </c>
       <c r="G52">
-        <v>-8.370679130714599</v>
+        <v>-9.291520614645036</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.334356312674053</v>
       </c>
       <c r="E53">
-        <v>-9.75115157200216</v>
+        <v>-14.30597224144914</v>
       </c>
       <c r="F53">
-        <v>-1.919399160393772</v>
+        <v>-1.242028344036378</v>
       </c>
       <c r="G53">
-        <v>-9.498568753762134</v>
+        <v>-8.891881488780836</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.438080364048829</v>
       </c>
       <c r="E54">
-        <v>-10.01344531500043</v>
+        <v>-13.53690150072649</v>
       </c>
       <c r="F54">
-        <v>-2.382424091478973</v>
+        <v>-0.3254933870059372</v>
       </c>
       <c r="G54">
-        <v>-10.08229738542859</v>
+        <v>-9.480834161308259</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.564768668234455</v>
       </c>
       <c r="E55">
-        <v>-9.580156393472526</v>
+        <v>-13.55151488634924</v>
       </c>
       <c r="F55">
-        <v>-2.160977660734906</v>
+        <v>-1.514870782854201</v>
       </c>
       <c r="G55">
-        <v>-8.717405807224626</v>
+        <v>-8.057988172893817</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.719816201848477</v>
       </c>
       <c r="E56">
-        <v>-8.055215413759573</v>
+        <v>-12.7979813399469</v>
       </c>
       <c r="F56">
-        <v>-1.999339092034452</v>
+        <v>-1.60772900364712</v>
       </c>
       <c r="G56">
-        <v>-9.262215665531407</v>
+        <v>-8.49930706709744</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.898785001411067</v>
       </c>
       <c r="E57">
-        <v>-8.207462709897451</v>
+        <v>-10.53772033629046</v>
       </c>
       <c r="F57">
-        <v>-2.297653856796203</v>
+        <v>-2.047545516394513</v>
       </c>
       <c r="G57">
-        <v>-8.992412825171884</v>
+        <v>-8.943138665365373</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.096770631328664</v>
       </c>
       <c r="E58">
-        <v>-6.979354144439272</v>
+        <v>-11.98285601856623</v>
       </c>
       <c r="F58">
-        <v>-2.399357866979809</v>
+        <v>-1.688822665047197</v>
       </c>
       <c r="G58">
-        <v>-8.886293287910547</v>
+        <v>-10.05974925976061</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.308756547675467</v>
       </c>
       <c r="E59">
-        <v>-5.844278548994674</v>
+        <v>-9.865558939331944</v>
       </c>
       <c r="F59">
-        <v>-2.112537639752317</v>
+        <v>-1.896902617864955</v>
       </c>
       <c r="G59">
-        <v>-8.832099657432677</v>
+        <v>-9.444189732734067</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.524795227036903</v>
       </c>
       <c r="E60">
-        <v>-6.279175078795304</v>
+        <v>-10.84806571698412</v>
       </c>
       <c r="F60">
-        <v>-2.725657507120333</v>
+        <v>-1.815788368287977</v>
       </c>
       <c r="G60">
-        <v>-9.309553156197447</v>
+        <v>-10.19905701605314</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.743892787164799</v>
       </c>
       <c r="E61">
-        <v>-6.971492713561956</v>
+        <v>-10.7518220588991</v>
       </c>
       <c r="F61">
-        <v>-2.460965610796319</v>
+        <v>-2.107092066962079</v>
       </c>
       <c r="G61">
-        <v>-9.347548287351662</v>
+        <v>-9.664989878021297</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.960924091164855</v>
       </c>
       <c r="E62">
-        <v>-4.944855683961226</v>
+        <v>-8.528830396325784</v>
       </c>
       <c r="F62">
-        <v>-2.677387734523654</v>
+        <v>-1.896919246777067</v>
       </c>
       <c r="G62">
-        <v>-9.582153407537653</v>
+        <v>-9.774820536832157</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.170355466351946</v>
       </c>
       <c r="E63">
-        <v>-5.243916107427776</v>
+        <v>-10.73845853210247</v>
       </c>
       <c r="F63">
-        <v>-2.856336208879862</v>
+        <v>-1.890544830467423</v>
       </c>
       <c r="G63">
-        <v>-9.856150709095434</v>
+        <v>-10.63504924248408</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.371162577486557</v>
       </c>
       <c r="E64">
-        <v>-4.393160752554762</v>
+        <v>-9.768323545439246</v>
       </c>
       <c r="F64">
-        <v>-2.653210880018556</v>
+        <v>-1.979568899239063</v>
       </c>
       <c r="G64">
-        <v>-10.06048089032479</v>
+        <v>-10.70638818830983</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.554419824024339</v>
       </c>
       <c r="E65">
-        <v>-4.494829522500969</v>
+        <v>-9.69295162405558</v>
       </c>
       <c r="F65">
-        <v>-2.959707069539467</v>
+        <v>-1.880321216930304</v>
       </c>
       <c r="G65">
-        <v>-9.598997463241465</v>
+        <v>-11.27185916132721</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.717112794112008</v>
       </c>
       <c r="E66">
-        <v>-4.171396851925136</v>
+        <v>-6.933630142383825</v>
       </c>
       <c r="F66">
-        <v>-3.374940507214452</v>
+        <v>-2.007407281820658</v>
       </c>
       <c r="G66">
-        <v>-10.087137403007</v>
+        <v>-9.869366406888204</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.852486636772013</v>
       </c>
       <c r="E67">
-        <v>-4.280854597164536</v>
+        <v>-9.136841430491637</v>
       </c>
       <c r="F67">
-        <v>-3.392704936467936</v>
+        <v>-2.373879998065177</v>
       </c>
       <c r="G67">
-        <v>-9.987384044817682</v>
+        <v>-10.52120620247962</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.948380204072216</v>
       </c>
       <c r="E68">
-        <v>-4.443290959819672</v>
+        <v>-8.982506507836224</v>
       </c>
       <c r="F68">
-        <v>-3.187724296126693</v>
+        <v>-2.253589615257974</v>
       </c>
       <c r="G68">
-        <v>-10.09011689399235</v>
+        <v>-10.53183636420622</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.997827030493964</v>
       </c>
       <c r="E69">
-        <v>-4.433744936611503</v>
+        <v>-8.441208952751371</v>
       </c>
       <c r="F69">
-        <v>-3.16336848285315</v>
+        <v>-2.226836071228455</v>
       </c>
       <c r="G69">
-        <v>-10.29247067953476</v>
+        <v>-10.50112774378394</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.989212611136351</v>
       </c>
       <c r="E70">
-        <v>-4.702713650297084</v>
+        <v>-8.978299555483098</v>
       </c>
       <c r="F70">
-        <v>-3.325619153889921</v>
+        <v>-2.176338816261711</v>
       </c>
       <c r="G70">
-        <v>-9.824710458108974</v>
+        <v>-9.980776195921298</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.920779430898043</v>
       </c>
       <c r="E71">
-        <v>-4.07699628276124</v>
+        <v>-7.701378568696241</v>
       </c>
       <c r="F71">
-        <v>-3.403556489400527</v>
+        <v>-2.286020744994343</v>
       </c>
       <c r="G71">
-        <v>-10.2525918479687</v>
+        <v>-9.544800522218058</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.793810441291098</v>
       </c>
       <c r="E72">
-        <v>-4.22935679074931</v>
+        <v>-8.292928599844213</v>
       </c>
       <c r="F72">
-        <v>-3.693882249671844</v>
+        <v>-2.39477383020757</v>
       </c>
       <c r="G72">
-        <v>-9.50776213872469</v>
+        <v>-10.18877777215371</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.610108711514211</v>
       </c>
       <c r="E73">
-        <v>-5.216718092537708</v>
+        <v>-9.957396392207498</v>
       </c>
       <c r="F73">
-        <v>-3.833352102967977</v>
+        <v>-2.86165666890278</v>
       </c>
       <c r="G73">
-        <v>-9.363210478297953</v>
+        <v>-8.658057657342113</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.382004735548855</v>
       </c>
       <c r="E74">
-        <v>-4.819720361707271</v>
+        <v>-10.27184457035211</v>
       </c>
       <c r="F74">
-        <v>-3.70259659147155</v>
+        <v>-2.817993896814115</v>
       </c>
       <c r="G74">
-        <v>-9.156897280290574</v>
+        <v>-8.392585010547956</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.119474391704202</v>
       </c>
       <c r="E75">
-        <v>-5.883599288803276</v>
+        <v>-9.603564075618175</v>
       </c>
       <c r="F75">
-        <v>-3.851498205347082</v>
+        <v>-2.670543749410083</v>
       </c>
       <c r="G75">
-        <v>-8.962131265124171</v>
+        <v>-9.813229486178782</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.838725139567773</v>
       </c>
       <c r="E76">
-        <v>-5.64090025283619</v>
+        <v>-10.87533618745831</v>
       </c>
       <c r="F76">
-        <v>-4.250847072690209</v>
+        <v>-3.164104114250871</v>
       </c>
       <c r="G76">
-        <v>-8.795534681951427</v>
+        <v>-9.217569648388796</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.558658026192757</v>
       </c>
       <c r="E77">
-        <v>-6.241611386901678</v>
+        <v>-10.07009652483639</v>
       </c>
       <c r="F77">
-        <v>-4.091384515917569</v>
+        <v>-3.385104731779742</v>
       </c>
       <c r="G77">
-        <v>-8.490822138880288</v>
+        <v>-7.906980948665501</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.290171215046115</v>
       </c>
       <c r="E78">
-        <v>-7.667659551235128</v>
+        <v>-10.50168274013741</v>
       </c>
       <c r="F78">
-        <v>-4.304561626224168</v>
+        <v>-3.182996933969106</v>
       </c>
       <c r="G78">
-        <v>-8.314035696537669</v>
+        <v>-8.646781939235355</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.047542961658075</v>
       </c>
       <c r="E79">
-        <v>-7.762988457570597</v>
+        <v>-10.74423686493625</v>
       </c>
       <c r="F79">
-        <v>-4.34958005057645</v>
+        <v>-3.06533629483449</v>
       </c>
       <c r="G79">
-        <v>-7.996928470967499</v>
+        <v>-8.432275141018279</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.836855461138347</v>
       </c>
       <c r="E80">
-        <v>-9.096252717960889</v>
+        <v>-11.60299856185483</v>
       </c>
       <c r="F80">
-        <v>-4.779291727730381</v>
+        <v>-3.780023973677384</v>
       </c>
       <c r="G80">
-        <v>-7.681155395249657</v>
+        <v>-8.322212744019668</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.660428810832014</v>
       </c>
       <c r="E81">
-        <v>-8.99755915543772</v>
+        <v>-11.58917765918342</v>
       </c>
       <c r="F81">
-        <v>-4.38648039840619</v>
+        <v>-3.391423718382345</v>
       </c>
       <c r="G81">
-        <v>-6.617013637106326</v>
+        <v>-8.505878499992894</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.522990864363519</v>
       </c>
       <c r="E82">
-        <v>-9.355679936912308</v>
+        <v>-12.75656391667275</v>
       </c>
       <c r="F82">
-        <v>-4.976844787328214</v>
+        <v>-3.704880295401614</v>
       </c>
       <c r="G82">
-        <v>-7.407316999877762</v>
+        <v>-7.904061047499864</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.418452954606696</v>
       </c>
       <c r="E83">
-        <v>-10.38878335465219</v>
+        <v>-12.63395095444106</v>
       </c>
       <c r="F83">
-        <v>-4.88692592471435</v>
+        <v>-3.857408595823502</v>
       </c>
       <c r="G83">
-        <v>-7.110476934099011</v>
+        <v>-7.912006356794115</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.347978255077705</v>
       </c>
       <c r="E84">
-        <v>-11.68087472936474</v>
+        <v>-12.42758839391153</v>
       </c>
       <c r="F84">
-        <v>-4.740616045569435</v>
+        <v>-3.986521804285619</v>
       </c>
       <c r="G84">
-        <v>-7.188403865547915</v>
+        <v>-8.837267419019479</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.313124668821686</v>
       </c>
       <c r="E85">
-        <v>-12.57359545286683</v>
+        <v>-16.43094508412644</v>
       </c>
       <c r="F85">
-        <v>-5.244485544066777</v>
+        <v>-4.021635731842742</v>
       </c>
       <c r="G85">
-        <v>-7.547108095819026</v>
+        <v>-7.828759378663602</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.314248328830165</v>
       </c>
       <c r="E86">
-        <v>-13.30775165899035</v>
+        <v>-16.43778760835202</v>
       </c>
       <c r="F86">
-        <v>-5.019915253404505</v>
+        <v>-3.688788259594833</v>
       </c>
       <c r="G86">
-        <v>-7.255144463619622</v>
+        <v>-7.875745951502477</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.363608291934338</v>
       </c>
       <c r="E87">
-        <v>-14.32087997788239</v>
+        <v>-18.40425480381284</v>
       </c>
       <c r="F87">
-        <v>-5.268876198870459</v>
+        <v>-3.750082429640086</v>
       </c>
       <c r="G87">
-        <v>-7.057524758198368</v>
+        <v>-7.871852749948294</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.468034697484716</v>
       </c>
       <c r="E88">
-        <v>-16.22550633229446</v>
+        <v>-19.3075223432788</v>
       </c>
       <c r="F88">
-        <v>-5.346042269600247</v>
+        <v>-4.543190474297796</v>
       </c>
       <c r="G88">
-        <v>-6.878007115785849</v>
+        <v>-7.154070197760134</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.637253080401957</v>
       </c>
       <c r="E89">
-        <v>-18.27604464770768</v>
+        <v>-21.01814887120227</v>
       </c>
       <c r="F89">
-        <v>-5.711707295827892</v>
+        <v>-4.22622598867583</v>
       </c>
       <c r="G89">
-        <v>-7.888094286363959</v>
+        <v>-7.684111712416225</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.885250194722804</v>
       </c>
       <c r="E90">
-        <v>-19.77553107502352</v>
+        <v>-22.61698548977239</v>
       </c>
       <c r="F90">
-        <v>-5.794288057082566</v>
+        <v>-4.075151530284314</v>
       </c>
       <c r="G90">
-        <v>-7.265218453695624</v>
+        <v>-7.723639626155124</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.214473888380642</v>
       </c>
       <c r="E91">
-        <v>-21.39373144845043</v>
+        <v>-24.18564435755539</v>
       </c>
       <c r="F91">
-        <v>-5.543649175199204</v>
+        <v>-4.031688305140994</v>
       </c>
       <c r="G91">
-        <v>-7.794614411971558</v>
+        <v>-7.955162628444054</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.636165609688981</v>
       </c>
       <c r="E92">
-        <v>-22.91746332560334</v>
+        <v>-26.04825553012429</v>
       </c>
       <c r="F92">
-        <v>-5.881632605730882</v>
+        <v>-4.420042294166182</v>
       </c>
       <c r="G92">
-        <v>-8.324884354269861</v>
+        <v>-8.414739181296758</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.154658148454315</v>
       </c>
       <c r="E93">
-        <v>-25.40693304115802</v>
+        <v>-28.76304852687863</v>
       </c>
       <c r="F93">
-        <v>-5.398549247373683</v>
+        <v>-4.299854852243483</v>
       </c>
       <c r="G93">
-        <v>-8.179733485100515</v>
+        <v>-8.357625649653253</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.764551475277901</v>
       </c>
       <c r="E94">
-        <v>-26.67506425989599</v>
+        <v>-29.55542732331876</v>
       </c>
       <c r="F94">
-        <v>-5.151347799179782</v>
+        <v>-4.656081783068066</v>
       </c>
       <c r="G94">
-        <v>-7.608485610117114</v>
+        <v>-7.974456487846926</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.468063726331864</v>
       </c>
       <c r="E95">
-        <v>-29.39504688786311</v>
+        <v>-29.6377481880672</v>
       </c>
       <c r="F95">
-        <v>-5.422409360695695</v>
+        <v>-3.403901737290093</v>
       </c>
       <c r="G95">
-        <v>-9.539715524269736</v>
+        <v>-9.489901745540323</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.255227308804311</v>
       </c>
       <c r="E96">
-        <v>-30.99771459544372</v>
+        <v>-33.50217355996379</v>
       </c>
       <c r="F96">
-        <v>-5.091140843245479</v>
+        <v>-4.021680867461332</v>
       </c>
       <c r="G96">
-        <v>-9.37662811936862</v>
+        <v>-7.471475372428837</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.104423622513078</v>
       </c>
       <c r="E97">
-        <v>-34.27584975875224</v>
+        <v>-34.78014062424641</v>
       </c>
       <c r="F97">
-        <v>-4.512978116548958</v>
+        <v>-3.900021370890231</v>
       </c>
       <c r="G97">
-        <v>-9.700720596026651</v>
+        <v>-8.488097559901469</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.013906238666729</v>
       </c>
       <c r="E98">
-        <v>-35.36634026335432</v>
+        <v>-37.9995052518834</v>
       </c>
       <c r="F98">
-        <v>-4.596719734239649</v>
+        <v>-3.582926229530241</v>
       </c>
       <c r="G98">
-        <v>-9.901826305900759</v>
+        <v>-10.06704570212917</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.924923763501424</v>
       </c>
       <c r="E99">
-        <v>-38.16812524579601</v>
+        <v>-39.57812223400927</v>
       </c>
       <c r="F99">
-        <v>-4.309600978447096</v>
+        <v>-3.714638299399594</v>
       </c>
       <c r="G99">
-        <v>-10.4308945201683</v>
+        <v>-9.196673484944917</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.8561474112988</v>
       </c>
       <c r="E100">
-        <v>-39.161149404331</v>
+        <v>-42.45973062778415</v>
       </c>
       <c r="F100">
-        <v>-4.087776041989239</v>
+        <v>-3.645892001169241</v>
       </c>
       <c r="G100">
-        <v>-11.4933975582697</v>
+        <v>-9.422181225988991</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.70670883845198</v>
       </c>
       <c r="E101">
-        <v>-42.01959918203066</v>
+        <v>-44.17683966624961</v>
       </c>
       <c r="F101">
-        <v>-3.853744692188133</v>
+        <v>-3.224092518768845</v>
       </c>
       <c r="G101">
-        <v>-11.03419178651739</v>
+        <v>-10.70338221296018</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.55512077103028</v>
       </c>
       <c r="E102">
-        <v>-45.44214738144379</v>
+        <v>-46.52037024995909</v>
       </c>
       <c r="F102">
-        <v>-3.555533660163843</v>
+        <v>-3.160859100830136</v>
       </c>
       <c r="G102">
-        <v>-10.59128051990938</v>
+        <v>-10.98501363253152</v>
       </c>
     </row>
   </sheetData>
